--- a/CodeSystem-pcor-questionnaire-catalogue.xlsx
+++ b/CodeSystem-pcor-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="98">
   <si>
     <t>Property</t>
   </si>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>14</t>
+    <t>19</t>
   </si>
   <si>
     <t>Level</t>
@@ -141,85 +141,172 @@
     <t>dem</t>
   </si>
   <si>
-    <t>PCOR-MII Demographie (DEM) — Sammelbogen aus OECD-, GI-PS- und CPCOR-Einzelitems</t>
+    <t>PCOR-MII Demographie (DEM)</t>
+  </si>
+  <si>
+    <t>Sammelbogen aus OECD-, GI-PS- und CPCOR-Einzelitems</t>
   </si>
   <si>
     <t>mhi</t>
   </si>
   <si>
-    <t>PCOR-MII Medical History (MHI) — Sammelbogen, mit AN-spezifischen Zusatzitems</t>
+    <t>PCOR-MII Medical History (MHI)</t>
+  </si>
+  <si>
+    <t>Sammelbogen, mit AN-spezifischen Zusatzitems</t>
   </si>
   <si>
     <t>opd-sfk</t>
   </si>
   <si>
-    <t>OPD-SFK — Strukturfragebogen, 12 Items</t>
+    <t>OPD-SFK</t>
+  </si>
+  <si>
+    <t>Strukturfragebogen, 12 Items</t>
   </si>
   <si>
     <t>wai</t>
   </si>
   <si>
-    <t>WAI / Work Ability Score — 3-Item-Kurzfassung (metadata-only)</t>
+    <t>WAI / Work Ability Score</t>
+  </si>
+  <si>
+    <t>3-Item-Kurzfassung (metadata-only)</t>
   </si>
   <si>
     <t>gsltpaq</t>
   </si>
   <si>
-    <t>GSLTPAQ — Godin-Shephard Leisure-Time Physical Activity Questionnaire, PCOR-MII-Eigenübersetzung</t>
+    <t>GSLTPAQ</t>
+  </si>
+  <si>
+    <t>Godin-Shephard Leisure-Time Physical Activity Questionnaire, PCOR-MII-Eigenübersetzung</t>
   </si>
   <si>
     <t>expect</t>
   </si>
   <si>
-    <t>EXPECT — drei NRS-Einzelitems zur Verlaufserwartung, kein standardisierter Fragebogen</t>
+    <t>EXPECT</t>
+  </si>
+  <si>
+    <t>Drei NRS-Einzelitems zur Verlaufserwartung, kein standardisierter Fragebogen</t>
   </si>
   <si>
     <t>ipq-s</t>
   </si>
   <si>
-    <t>IPQ-S — die offene Ursachenfrage des B-IPQ, Einzelitem</t>
+    <t>IPQ-S</t>
+  </si>
+  <si>
+    <t>Die offene Ursachenfrage des B-IPQ, Einzelitem</t>
   </si>
   <si>
     <t>erq-6</t>
   </si>
   <si>
-    <t>ERQ-6 — 6-Item-Zuschnitt des Emotion Regulation Questionnaire (ERQ-Items 1, 2, 3, 6, 8, 9); nicht der ERQ-S</t>
+    <t>ERQ-6</t>
+  </si>
+  <si>
+    <t>6-Item-Zuschnitt des Emotion Regulation Questionnaire (ERQ-Items 1, 2, 3, 6, 8, 9); nicht der ERQ-S</t>
   </si>
   <si>
     <t>ede-q6</t>
   </si>
   <si>
-    <t>EDE-Q6 — 6-Item-Zuschnitt des Eating Disorder Examination-Questionnaire</t>
+    <t>EDE-Q6</t>
+  </si>
+  <si>
+    <t>6-Item-Zuschnitt des Eating Disorder Examination-Questionnaire</t>
   </si>
   <si>
     <t>ansocq-2</t>
   </si>
   <si>
-    <t>ANSOCQ-2 — 2-Item-Zuschnitt des Anorexia Nervosa Stages of Change Questionnaire</t>
+    <t>ANSOCQ-2</t>
+  </si>
+  <si>
+    <t>2-Item-Zuschnitt des Anorexia Nervosa Stages of Change Questionnaire</t>
   </si>
   <si>
     <t>ssuk-2</t>
   </si>
   <si>
-    <t>SSUK-2 — 2-Item-Zuschnitt der Skalen zur Sozialen Unterstützung bei Krankheit</t>
+    <t>SSUK-2</t>
+  </si>
+  <si>
+    <t>2-Item-Zuschnitt der Skalen zur Sozialen Unterstützung bei Krankheit</t>
   </si>
   <si>
     <t>ace</t>
   </si>
   <si>
-    <t>ACE + Zeitangaben — die ersten fünf Fragen des Adverse Childhood Experiences Questionnaire plus die sechs UKHD-Items zur zeitlichen Einordnung (PCOR-MII-Komposit)</t>
-  </si>
-  <si>
-    <t>ukhd-an</t>
-  </si>
-  <si>
-    <t>UKHD-AN — Sammelbogen der standortspezifischen AN-Zusatzitems des Universitätsklinikums Heidelberg, sechs Dictionary-Gruppen</t>
+    <t>ACE + Zeitangaben</t>
+  </si>
+  <si>
+    <t>Die ersten fünf Fragen des Adverse Childhood Experiences Questionnaire plus die sechs UKHD-Items zur zeitlichen Einordnung (PCOR-MII-Komposit)</t>
+  </si>
+  <si>
+    <t>ukhd-pt</t>
+  </si>
+  <si>
+    <t>UKHD-PT</t>
+  </si>
+  <si>
+    <t>Vorbehandlung, 2 Items (UKHD-Zusatzitems AN)</t>
+  </si>
+  <si>
+    <t>ukhd-anb</t>
+  </si>
+  <si>
+    <t>UKHD-ANB</t>
+  </si>
+  <si>
+    <t>Essstörungsanamnese, 2 zusammengesetzte Items (UKHD-Zusatzitems AN)</t>
+  </si>
+  <si>
+    <t>ukhd-ct</t>
+  </si>
+  <si>
+    <t>UKHD-CT</t>
+  </si>
+  <si>
+    <t>Aktuelle Behandlung, 1 Item (UKHD-Zusatzitems AN)</t>
+  </si>
+  <si>
+    <t>ukhd-le</t>
+  </si>
+  <si>
+    <t>UKHD-LE</t>
+  </si>
+  <si>
+    <t>Belastende Lebensereignisse, 4 Items (UKHD-Zusatzitems AN)</t>
+  </si>
+  <si>
+    <t>ukhd-nd</t>
+  </si>
+  <si>
+    <t>UKHD-ND</t>
+  </si>
+  <si>
+    <t>Neue Diagnosen, 3 Items (UKHD-Zusatzitems AN)</t>
+  </si>
+  <si>
+    <t>ukhd-d</t>
+  </si>
+  <si>
+    <t>UKHD-D</t>
+  </si>
+  <si>
+    <t>Diagnosen bei Aufnahme, 2 Items (UKHD-Zusatzitems AN; Dictionary-Schreibweise UKHD_D)</t>
   </si>
   <si>
     <t>ukhd-edp</t>
   </si>
   <si>
-    <t>UKHD-EDP — 11 Items zur Essstörungspathologie, vermutlich EDI-2-Zuschnitt (metadata-only)</t>
+    <t>UKHD-EDP</t>
+  </si>
+  <si>
+    <t>11 Items zur Essstörungspathologie, vermutlich EDI-2-Zuschnitt (metadata-only)</t>
   </si>
 </sst>
 </file>
@@ -529,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -556,163 +643,261 @@
       <c r="C2" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>67</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>73</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>79</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
         <v>40</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-pcor-questionnaire-catalogue.xlsx
+++ b/CodeSystem-pcor-questionnaire-catalogue.xlsx
@@ -180,7 +180,7 @@
     <t>GSLTPAQ</t>
   </si>
   <si>
-    <t>Godin-Shephard Leisure-Time Physical Activity Questionnaire, PCOR-MII-Eigenübersetzung</t>
+    <t>Godin-Shephard Leisure-Time Physical Activity Questionnaire, deutsche Übersetzung aus SOMACROSS 2.0 (UKE)</t>
   </si>
   <si>
     <t>expect</t>

--- a/CodeSystem-pcor-questionnaire-catalogue.xlsx
+++ b/CodeSystem-pcor-questionnaire-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>Level</t>
@@ -181,6 +181,15 @@
   </si>
   <si>
     <t>Godin-Shephard Leisure-Time Physical Activity Questionnaire, deutsche Übersetzung aus SOMACROSS 2.0 (UKE)</t>
+  </si>
+  <si>
+    <t>promis-gh</t>
+  </si>
+  <si>
+    <t>PROMIS-GH</t>
+  </si>
+  <si>
+    <t>PROMIS Global Health, 2-Item-Zuschnitt (Global01, Global02) — Übergangslösung bis zur Aufnahme der 10-Item-Skala ins MII-PRO-Modul</t>
   </si>
   <si>
     <t>expect</t>
@@ -616,7 +625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -899,6 +908,20 @@
         <v>97</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
